--- a/assets/template/year2.xlsx
+++ b/assets/template/year2.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\qc\assets\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33F54667-9E95-4529-9D51-A034EABEF287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B2866F-0B51-4DF8-98C9-3659D4A364BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,18 +39,10 @@
     <t>241001</t>
   </si>
   <si>
-    <t>Khu vực
-Area</t>
-  </si>
-  <si>
     <t xml:space="preserve">KẾ HOẠCH NGHIÊN CỨU ĐỘ ỔN ĐỊNH HÀNG NĂM
 ANNUAL PLAN FOR STABILITY STUDY </t>
   </si>
   <si>
-    <t>Năm
-Year</t>
-  </si>
-  <si>
     <t>Stt
 S. No</t>
   </si>
@@ -77,6 +69,12 @@
   <si>
     <t>Người phê duyệt / Ngày
 Approved by / Date</t>
+  </si>
+  <si>
+    <t>Khu vực/ Area</t>
+  </si>
+  <si>
+    <t>Năm/ Year</t>
   </si>
 </sst>
 </file>
@@ -109,18 +107,6 @@
       <family val="1"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
@@ -141,6 +127,18 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -299,60 +297,60 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -376,23 +374,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>200025</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>485775</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>219075</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1285875</xdr:colOff>
+      <xdr:colOff>1322069</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>137632</xdr:rowOff>
+      <xdr:rowOff>220980</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAAA058A-5886-4B79-845A-5E6A6C8E1689}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5B59ACC9-5270-470E-A47D-071854607085}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -415,8 +413,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="695325" y="219075"/>
-          <a:ext cx="1085850" cy="451957"/>
+          <a:off x="485775" y="152400"/>
+          <a:ext cx="1331594" cy="601980"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -700,17 +698,17 @@
   <cols>
     <col min="1" max="1" width="5.77734375" style="8" customWidth="1"/>
     <col min="2" max="2" width="21.44140625" style="8" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="8" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" style="8" customWidth="1"/>
     <col min="5" max="5" width="11.109375" style="8" customWidth="1"/>
     <col min="6" max="16384" width="8.77734375" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="13" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="12" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="20"/>
       <c r="B1" s="21"/>
       <c r="C1" s="24" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D1" s="24"/>
       <c r="E1" s="24"/>
@@ -724,30 +722,30 @@
       <c r="M1" s="24"/>
       <c r="N1" s="24"/>
       <c r="O1" s="24"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-    </row>
-    <row r="2" spans="1:33" s="13" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P1" s="10"/>
+      <c r="Q1" s="11"/>
+      <c r="R1" s="11"/>
+      <c r="S1" s="11"/>
+      <c r="T1" s="11"/>
+      <c r="U1" s="11"/>
+      <c r="V1" s="11"/>
+      <c r="W1" s="11"/>
+      <c r="X1" s="11"/>
+      <c r="Y1" s="11"/>
+      <c r="Z1" s="11"/>
+      <c r="AA1" s="11"/>
+      <c r="AB1" s="11"/>
+      <c r="AC1" s="11"/>
+      <c r="AD1" s="11"/>
+      <c r="AE1" s="11"/>
+      <c r="AF1" s="11"/>
+      <c r="AG1" s="11"/>
+    </row>
+    <row r="2" spans="1:33" s="12" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="22"/>
       <c r="B2" s="23"/>
-      <c r="C2" s="9" t="s">
-        <v>3</v>
+      <c r="C2" s="16" t="s">
+        <v>11</v>
       </c>
       <c r="D2" s="24"/>
       <c r="E2" s="24"/>
@@ -759,55 +757,55 @@
       <c r="K2" s="24"/>
       <c r="L2" s="24"/>
       <c r="M2" s="24"/>
-      <c r="N2" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="O2" s="10"/>
-      <c r="P2" s="12"/>
-      <c r="Q2" s="12"/>
-      <c r="R2" s="12"/>
-      <c r="S2" s="12"/>
-      <c r="T2" s="12"/>
-      <c r="U2" s="12"/>
-      <c r="V2" s="12"/>
-      <c r="W2" s="12"/>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="12"/>
-      <c r="Z2" s="12"/>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="12"/>
-      <c r="AC2" s="12"/>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="12"/>
-      <c r="AF2" s="12"/>
-      <c r="AG2" s="12"/>
+      <c r="N2" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="O2" s="9"/>
+      <c r="P2" s="11"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="11"/>
+      <c r="S2" s="11"/>
+      <c r="T2" s="11"/>
+      <c r="U2" s="11"/>
+      <c r="V2" s="11"/>
+      <c r="W2" s="11"/>
+      <c r="X2" s="11"/>
+      <c r="Y2" s="11"/>
+      <c r="Z2" s="11"/>
+      <c r="AA2" s="11"/>
+      <c r="AB2" s="11"/>
+      <c r="AC2" s="11"/>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="11"/>
+      <c r="AF2" s="11"/>
+      <c r="AG2" s="11"/>
     </row>
     <row r="3" spans="1:33" s="2" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="D3" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="25" t="s">
+      <c r="E3" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="25" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="25" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="15"/>
-      <c r="O3" s="15"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
+      <c r="O3" s="14"/>
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
@@ -817,7 +815,7 @@
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
     </row>
-    <row r="4" spans="1:33" s="3" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" s="3" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="26"/>
       <c r="C4" s="26"/>
@@ -832,7 +830,7 @@
       <c r="V4" s="5"/>
       <c r="W4" s="5"/>
     </row>
-    <row r="5" spans="1:33" s="3" customFormat="1" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" s="3" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="27"/>
       <c r="B5" s="27"/>
       <c r="C5" s="27"/>
@@ -848,7 +846,7 @@
       <c r="W5" s="5"/>
     </row>
     <row r="6" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A6" s="15"/>
+      <c r="A6" s="14"/>
       <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
@@ -861,16 +859,16 @@
       <c r="E6" s="7">
         <v>2101010011</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="13"/>
+      <c r="L6" s="13"/>
+      <c r="M6" s="13"/>
+      <c r="N6" s="13"/>
+      <c r="O6" s="13"/>
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
@@ -881,21 +879,21 @@
       <c r="W6" s="4"/>
     </row>
     <row r="7" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A7" s="15"/>
+      <c r="A7" s="14"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
-      <c r="F7" s="14"/>
-      <c r="G7" s="14"/>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="13"/>
+      <c r="L7" s="13"/>
+      <c r="M7" s="13"/>
+      <c r="N7" s="13"/>
+      <c r="O7" s="13"/>
       <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
@@ -906,17 +904,17 @@
       <c r="W7" s="4"/>
     </row>
     <row r="8" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A8" s="15"/>
-      <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="14"/>
-      <c r="N8" s="14"/>
-      <c r="O8" s="14"/>
+      <c r="A8" s="14"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="13"/>
+      <c r="L8" s="13"/>
+      <c r="M8" s="13"/>
+      <c r="N8" s="13"/>
+      <c r="O8" s="13"/>
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
@@ -927,17 +925,17 @@
       <c r="W8" s="4"/>
     </row>
     <row r="9" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A9" s="15"/>
-      <c r="F9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
+      <c r="A9" s="14"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
+      <c r="O9" s="13"/>
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
@@ -948,17 +946,17 @@
       <c r="W9" s="4"/>
     </row>
     <row r="10" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A10" s="15"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
+      <c r="A10" s="14"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
+      <c r="N10" s="13"/>
+      <c r="O10" s="13"/>
       <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
@@ -969,17 +967,17 @@
       <c r="W10" s="4"/>
     </row>
     <row r="11" spans="1:33" s="2" customFormat="1" ht="15" x14ac:dyDescent="0.25">
-      <c r="A11" s="15"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="14"/>
-      <c r="N11" s="14"/>
-      <c r="O11" s="14"/>
+      <c r="A11" s="14"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
@@ -991,25 +989,25 @@
     </row>
     <row r="12" spans="1:33" s="1" customFormat="1" ht="15" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:33" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="16"/>
+      <c r="A13" s="15"/>
       <c r="B13" s="17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
       <c r="F13" s="18"/>
       <c r="G13" s="17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
       <c r="J13" s="18"/>
       <c r="K13" s="18"/>
-      <c r="P13" s="16"/>
+      <c r="P13" s="15"/>
     </row>
     <row r="14" spans="1:33" customFormat="1" ht="159" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="16"/>
+      <c r="A14" s="15"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
       <c r="D14" s="19"/>
@@ -1020,7 +1018,7 @@
       <c r="I14" s="19"/>
       <c r="J14" s="19"/>
       <c r="K14" s="19"/>
-      <c r="P14" s="16"/>
+      <c r="P14" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -1042,7 +1040,7 @@
   <headerFooter>
     <oddHeader xml:space="preserve">&amp;C&amp;12
 </oddHeader>
-    <oddFooter>&amp;L&amp;12Mã số phụ lục / Appendix No. 0002020_A02_03&amp;C&amp;12Ngày hiệu lực / Appendix effective 28/05/2024&amp;R&amp;12Trang / Page &amp;P/&amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;12Mã số phụ lục / Appendix No. 0002020_A02_04&amp;C&amp;12Ngày hiệu lực / Appendix effective 04/09/2026&amp;R&amp;12Trang / Page &amp;P/&amp;N</oddFooter>
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
